--- a/MP-relecture/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/MP-relecture/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-30T11:26:53+00:00</t>
+    <t>2024-09-30T11:27:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
